--- a/benchmark/data/siRNA_bench/mutual_KIT.xlsx
+++ b/benchmark/data/siRNA_bench/mutual_KIT.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>BioRedis_engine</t>
+          <t>BIOREDIS_engine</t>
         </is>
       </c>
     </row>

--- a/benchmark/data/siRNA_bench/mutual_KIT.xlsx
+++ b/benchmark/data/siRNA_bench/mutual_KIT.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,97 +417,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>RNAi_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>RNAi_seq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>e-value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>bit_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>alignment_length</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>target_seq</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>target_gene_name</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>specificity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>complemenatry_regions</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>complemenatry_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>RNAi_sense</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>repeated_motif</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>repeated_motif_pct</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>GC%</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -608,7 +596,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -695,7 +683,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -782,7 +770,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -869,7 +857,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -956,7 +944,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1031,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1118,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1205,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1292,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1379,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>BIOREDIS_engine</t>
+          <t>BIOREDIS</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1462,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1545,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1628,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1711,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1794,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1877,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1960,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2043,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2126,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2209,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Eurofinsgenomics</t>
+          <t>Eurofins_Genomics</t>
         </is>
       </c>
     </row>
